--- a/data/trans_orig/P33B5_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P33B5_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que toma algún remedio para dormir (no medicamentos) en 2023</t>
+          <t>Población según la frecuencia con la que toma algún remedio para dormir (no medicamentos) en 2023 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47920</t>
+          <t>46318</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>72727</t>
+          <t>72808</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>135646</t>
+          <t>136555</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>171894</t>
+          <t>172661</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>189708</t>
+          <t>190014</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>234210</t>
+          <t>235813</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,62%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10181</t>
+          <t>9991</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22743</t>
+          <t>22879</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39499</t>
+          <t>40592</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59928</t>
+          <t>59105</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53230</t>
+          <t>53922</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>76378</t>
+          <t>76657</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18390</t>
+          <t>18691</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38398</t>
+          <t>37780</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58089</t>
+          <t>58301</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>80978</t>
+          <t>82954</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>83119</t>
+          <t>82488</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>112982</t>
+          <t>111840</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>394937</t>
+          <t>396004</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>427656</t>
+          <t>429855</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>461381</t>
+          <t>460969</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>501351</t>
+          <t>502575</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>866284</t>
+          <t>866155</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>922510</t>
+          <t>920270</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>72,66%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>51982</t>
+          <t>51342</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>98092</t>
+          <t>96792</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>85068</t>
+          <t>86574</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>143332</t>
+          <t>142963</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>156261</t>
+          <t>157075</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>228644</t>
+          <t>226582</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21987</t>
+          <t>21637</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49111</t>
+          <t>48617</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40768</t>
+          <t>41594</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72456</t>
+          <t>71568</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>69506</t>
+          <t>69207</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>112575</t>
+          <t>110883</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>96399</t>
+          <t>98819</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>167781</t>
+          <t>170491</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>139762</t>
+          <t>129434</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>219764</t>
+          <t>216778</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>257251</t>
+          <t>264335</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>370624</t>
+          <t>370549</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1996759</t>
+          <t>1993540</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2112147</t>
+          <t>2112162</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1819977</t>
+          <t>1822534</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1970070</t>
+          <t>1983141</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3839985</t>
+          <t>3843307</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4044263</t>
+          <t>4029597</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,02%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16143</t>
+          <t>15622</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36153</t>
+          <t>35096</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>24683</t>
+          <t>24038</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43145</t>
+          <t>42808</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>45506</t>
+          <t>43497</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>72626</t>
+          <t>70844</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6455</t>
+          <t>7335</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20076</t>
+          <t>20198</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11432</t>
+          <t>10777</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24460</t>
+          <t>24913</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>20738</t>
+          <t>20490</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>38729</t>
+          <t>38706</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29983</t>
+          <t>29673</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55932</t>
+          <t>54110</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40172</t>
+          <t>41285</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>63333</t>
+          <t>62976</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>76779</t>
+          <t>77733</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>110754</t>
+          <t>112107</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>550412</t>
+          <t>551905</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>584640</t>
+          <t>584341</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>543187</t>
+          <t>542712</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>574225</t>
+          <t>574426</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1107279</t>
+          <t>1105948</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1149881</t>
+          <t>1151161</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>88,07%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>122914</t>
+          <t>121686</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>185471</t>
+          <t>184812</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>245965</t>
+          <t>246656</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>336391</t>
+          <t>340375</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>398265</t>
+          <t>398448</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>513130</t>
+          <t>510129</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>44130</t>
+          <t>43445</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>79361</t>
+          <t>77815</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>99883</t>
+          <t>99806</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>143070</t>
+          <t>144528</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>157591</t>
+          <t>155790</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>210105</t>
+          <t>210604</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>155803</t>
+          <t>160653</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>241674</t>
+          <t>241252</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>252933</t>
+          <t>252989</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>341788</t>
+          <t>338808</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>445379</t>
+          <t>440367</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>558751</t>
+          <t>561937</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2972225</t>
+          <t>2972785</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3123422</t>
+          <t>3113820</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2848706</t>
+          <t>2853536</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3056194</t>
+          <t>3053696</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5853339</t>
+          <t>5852294</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6076348</t>
+          <t>6102718</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,95%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33B5_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P33B5_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>58683</t>
+          <t>63538</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>46318</t>
+          <t>49772</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>72808</t>
+          <t>77896</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>151964</t>
+          <t>163825</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>136555</t>
+          <t>147321</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>172661</t>
+          <t>182062</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>210647</t>
+          <t>227362</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>190014</t>
+          <t>205634</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>235813</t>
+          <t>251239</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>17,97%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15417</t>
+          <t>16675</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9991</t>
+          <t>11021</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22879</t>
+          <t>24824</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>48976</t>
+          <t>54985</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40592</t>
+          <t>44967</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59105</t>
+          <t>67411</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>64393</t>
+          <t>71660</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53922</t>
+          <t>60434</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>76657</t>
+          <t>86044</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>27172</t>
+          <t>28632</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18691</t>
+          <t>20017</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>37780</t>
+          <t>40121</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>69107</t>
+          <t>74828</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58301</t>
+          <t>62879</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>82954</t>
+          <t>87834</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>96280</t>
+          <t>103459</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>82488</t>
+          <t>88330</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>111840</t>
+          <t>119000</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>412670</t>
+          <t>468698</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>396004</t>
+          <t>449348</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>429855</t>
+          <t>484403</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>482555</t>
+          <t>527081</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>460969</t>
+          <t>506585</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>502575</t>
+          <t>547846</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>895224</t>
+          <t>995779</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>866155</t>
+          <t>964119</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>920270</t>
+          <t>1024237</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>73,25%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>752603</t>
+          <t>820719</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>752603</t>
+          <t>820719</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>752603</t>
+          <t>820719</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1266544</t>
+          <t>1398261</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1266544</t>
+          <t>1398261</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1266544</t>
+          <t>1398261</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>75992</t>
+          <t>83780</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>51342</t>
+          <t>67090</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>96792</t>
+          <t>102902</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>118678</t>
+          <t>131342</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>86574</t>
+          <t>114767</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>142963</t>
+          <t>153117</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>194670</t>
+          <t>215122</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>157075</t>
+          <t>190247</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>226582</t>
+          <t>242153</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>32938</t>
+          <t>35527</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21637</t>
+          <t>24704</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48617</t>
+          <t>49806</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>57122</t>
+          <t>66274</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41594</t>
+          <t>55042</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>71568</t>
+          <t>82555</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>90060</t>
+          <t>101801</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>69207</t>
+          <t>84496</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>110883</t>
+          <t>120634</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>139256</t>
+          <t>154608</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>98819</t>
+          <t>132969</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>170491</t>
+          <t>181241</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>184821</t>
+          <t>205467</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>129434</t>
+          <t>183851</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>216778</t>
+          <t>229037</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>324077</t>
+          <t>360075</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>264335</t>
+          <t>329167</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>370549</t>
+          <t>397550</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2041111</t>
+          <t>1955570</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1993540</t>
+          <t>1922091</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2112162</t>
+          <t>1985288</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1876612</t>
+          <t>1767639</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1822534</t>
+          <t>1734423</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1983141</t>
+          <t>1796902</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>3917724</t>
+          <t>3723209</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3843307</t>
+          <t>3677890</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4029597</t>
+          <t>3767389</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>85,62%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2289297</t>
+          <t>2229485</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2289297</t>
+          <t>2229485</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2289297</t>
+          <t>2229485</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2237233</t>
+          <t>2170723</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2237233</t>
+          <t>2170723</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2237233</t>
+          <t>2170723</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4526531</t>
+          <t>4400208</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4526531</t>
+          <t>4400208</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4526531</t>
+          <t>4400208</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>23975</t>
+          <t>25215</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15622</t>
+          <t>15737</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35096</t>
+          <t>36310</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>32719</t>
+          <t>37313</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>24038</t>
+          <t>28635</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>42808</t>
+          <t>49270</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>56694</t>
+          <t>62528</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>43497</t>
+          <t>49633</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>70844</t>
+          <t>79298</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11911</t>
+          <t>12842</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7335</t>
+          <t>7547</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20198</t>
+          <t>21507</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16899</t>
+          <t>19153</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10777</t>
+          <t>12956</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24913</t>
+          <t>26924</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>28810</t>
+          <t>31995</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>20490</t>
+          <t>23442</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>38706</t>
+          <t>44493</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>41207</t>
+          <t>44811</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29673</t>
+          <t>33100</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54110</t>
+          <t>59441</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>51231</t>
+          <t>54820</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>41285</t>
+          <t>44197</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62976</t>
+          <t>67974</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>92438</t>
+          <t>99631</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>77733</t>
+          <t>83689</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>112107</t>
+          <t>118182</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>569530</t>
+          <t>628719</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>551905</t>
+          <t>610519</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>584341</t>
+          <t>646090</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>559614</t>
+          <t>623591</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>542712</t>
+          <t>604401</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>574426</t>
+          <t>638390</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1129144</t>
+          <t>1252310</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1105948</t>
+          <t>1228323</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1151161</t>
+          <t>1272832</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>88,0%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>158650</t>
+          <t>172532</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>121686</t>
+          <t>147233</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>184812</t>
+          <t>196452</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>303362</t>
+          <t>332480</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>246656</t>
+          <t>301820</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>340375</t>
+          <t>361727</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>462011</t>
+          <t>505013</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>398448</t>
+          <t>466918</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>510129</t>
+          <t>546851</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>60266</t>
+          <t>65044</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>43445</t>
+          <t>51251</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>77815</t>
+          <t>83398</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>122996</t>
+          <t>140413</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>99806</t>
+          <t>122521</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>144528</t>
+          <t>161908</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>183262</t>
+          <t>205456</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>155790</t>
+          <t>181852</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>210604</t>
+          <t>231618</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>207635</t>
+          <t>228051</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>160653</t>
+          <t>198180</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>241252</t>
+          <t>256952</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>305160</t>
+          <t>335115</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>252989</t>
+          <t>307643</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>338808</t>
+          <t>363116</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>512795</t>
+          <t>563166</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>440367</t>
+          <t>525105</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>561937</t>
+          <t>607565</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3023312</t>
+          <t>3052987</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2972785</t>
+          <t>3013274</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3113820</t>
+          <t>3093624</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2918782</t>
+          <t>2918312</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2853536</t>
+          <t>2874707</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3053696</t>
+          <t>2959025</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>78,32%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>5942093</t>
+          <t>5971298</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5852294</t>
+          <t>5911461</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6102718</t>
+          <t>6029013</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>83,22%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3449863</t>
+          <t>3518614</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3449863</t>
+          <t>3518614</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3449863</t>
+          <t>3518614</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3650299</t>
+          <t>3726320</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3650299</t>
+          <t>3726320</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3650299</t>
+          <t>3726320</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7100161</t>
+          <t>7244933</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7100161</t>
+          <t>7244933</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7100161</t>
+          <t>7244933</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
